--- a/tame_output/ON/bt/strategyON_20240216.xlsx
+++ b/tame_output/ON/bt/strategyON_20240216.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -615,11 +615,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>22.5%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>76.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.3%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-2.8%</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>127.4%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1405,11 +1405,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>120.9%</t>
+          <t>120.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1874"/>
+  <dimension ref="A1:G1875"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.506593302686997</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44663,6 +44663,29 @@
       </c>
       <c r="G1874" t="n">
         <v>4.475510172066778</v>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" s="2" t="n">
+        <v>45337</v>
+      </c>
+      <c r="B1875" t="n">
+        <v>3.505294946706487</v>
+      </c>
+      <c r="C1875" t="n">
+        <v>3.128871588193264</v>
+      </c>
+      <c r="D1875" t="n">
+        <v>1.587286963911707</v>
+      </c>
+      <c r="E1875" t="n">
+        <v>3.763429949444199</v>
+      </c>
+      <c r="F1875" t="n">
+        <v>2.244621663599389</v>
+      </c>
+      <c r="G1875" t="n">
+        <v>4.475644586352897</v>
       </c>
     </row>
   </sheetData>
